--- a/Compititor's_Price/IKO_Prices/IKO_Prices_02-08-2026.xlsx
+++ b/Compititor's_Price/IKO_Prices/IKO_Prices_02-08-2026.xlsx
@@ -1,20 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Priyanka\Documents\Price_Comp_Dashboard\Compititor's_Price\IKO_Prices\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC9948C7-C27E-4B1E-8967-42BF428C2AB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="33375" yWindow="2220" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="68">
   <si>
     <t>SKU</t>
   </si>
@@ -133,132 +139,27 @@
     <t>IKO Enertherm ALU 150mm x 2.4m x 1.2m</t>
   </si>
   <si>
-    <t>Error: HTTPSConnectionPool(host='insulation4less.co.uk', port=443): Max retries exceeded with url: /products/iko-enertherm-alu-25mm-x-2-4m-x-1-2m (Caused by ResponseError('too many 429 error responses'))</t>
-  </si>
-  <si>
-    <t>Error: HTTPSConnectionPool(host='insulation4less.co.uk', port=443): Max retries exceeded with url: /products/iko-enertherm-alu-30mm-x-2-4m-x-1-2m (Caused by ResponseError('too many 429 error responses'))</t>
-  </si>
-  <si>
     <t>£21.95</t>
   </si>
   <si>
     <t>£23.15</t>
   </si>
   <si>
-    <t>Error: HTTPSConnectionPool(host='insulation4less.co.uk', port=443): Max retries exceeded with url: /products/iko-enertherm-alu-60mm-x-2-4m-x-1-2m (Caused by ResponseError('too many 429 error responses'))</t>
-  </si>
-  <si>
-    <t>Error: HTTPSConnectionPool(host='insulation4less.co.uk', port=443): Max retries exceeded with url: /products/iko-enertherm-alu-70mm-x-2-4m-x-1-2m (Caused by ResponseError('too many 429 error responses'))</t>
-  </si>
-  <si>
-    <t>Error: HTTPSConnectionPool(host='insulation4less.co.uk', port=443): Max retries exceeded with url: /products/iko-enertherm-alu-75mm-x-2-4m-x-1-2m (Caused by ResponseError('too many 429 error responses'))</t>
-  </si>
-  <si>
     <t>£36.45</t>
   </si>
   <si>
-    <t>Error: HTTPSConnectionPool(host='insulation4less.co.uk', port=443): Max retries exceeded with url: /products/iko-enertherm-alu-90mm-x-2-4m-x-1-2m (Caused by ResponseError('too many 429 error responses'))</t>
-  </si>
-  <si>
-    <t>Error: HTTPSConnectionPool(host='insulation4less.co.uk', port=443): Max retries exceeded with url: /products/iko-enertherm-alu-100mm-x-2-4m-x-1-2m (Caused by ResponseError('too many 429 error responses'))</t>
-  </si>
-  <si>
-    <t>Error: HTTPSConnectionPool(host='insulation4less.co.uk', port=443): Max retries exceeded with url: /products/iko-enertherm-alu-110mm-x-2-4m-x-1-2m (Caused by ResponseError('too many 429 error responses'))</t>
-  </si>
-  <si>
-    <t>Error: HTTPSConnectionPool(host='insulation4less.co.uk', port=443): Max retries exceeded with url: /products/iko-enertherm-alu-120mm-x-2-4m-x-1-2m (Caused by ResponseError('too many 429 error responses'))</t>
-  </si>
-  <si>
-    <t>Error: HTTPSConnectionPool(host='insulation4less.co.uk', port=443): Max retries exceeded with url: /products/iko-enertherm-alu-140mm-x-2-4m-x-1-2m (Caused by ResponseError('too many 429 error responses'))</t>
-  </si>
-  <si>
-    <t>Error: HTTPSConnectionPool(host='insulation4less.co.uk', port=443): Max retries exceeded with url: /products/iko-enertherm-alu-150mm-x-2-4m-x-1-2m (Caused by ResponseError('too many 429 error responses'))</t>
-  </si>
-  <si>
-    <t>Error: HTTPSConnectionPool(host='build4less.co.uk', port=443): Max retries exceeded with url: /products/iko-enertherm-alu-25mm-x-2-4m-x-1-2m (Caused by ResponseError('too many 429 error responses'))</t>
-  </si>
-  <si>
-    <t>Error: HTTPSConnectionPool(host='build4less.co.uk', port=443): Max retries exceeded with url: /products/iko-enertherm-alu-30mm-x-2-4m-x-1-2m (Caused by ResponseError('too many 429 error responses'))</t>
-  </si>
-  <si>
-    <t>Error: HTTPSConnectionPool(host='build4less.co.uk', port=443): Max retries exceeded with url: /products/iko-enertherm-alu-40mm-x-2-4m-x-1-2m (Caused by ResponseError('too many 429 error responses'))</t>
-  </si>
-  <si>
-    <t>Error: HTTPSConnectionPool(host='build4less.co.uk', port=443): Max retries exceeded with url: /products/iko-enertherm-alu-50mm-x-2-4m-x-1-2m (Caused by ResponseError('too many 429 error responses'))</t>
-  </si>
-  <si>
-    <t>Error: HTTPSConnectionPool(host='build4less.co.uk', port=443): Max retries exceeded with url: /products/iko-enertherm-alu-60mm-x-2-4m-x-1-2m (Caused by ResponseError('too many 429 error responses'))</t>
-  </si>
-  <si>
-    <t>Error: HTTPSConnectionPool(host='build4less.co.uk', port=443): Max retries exceeded with url: /products/iko-enertherm-alu-70mm-x-2-4m-x-1-2m (Caused by ResponseError('too many 429 error responses'))</t>
-  </si>
-  <si>
-    <t>Error: HTTPSConnectionPool(host='build4less.co.uk', port=443): Max retries exceeded with url: /products/iko-enertherm-alu-75mm-x-2-4m-x-1-2m (Caused by ResponseError('too many 429 error responses'))</t>
-  </si>
-  <si>
-    <t>Error: HTTPSConnectionPool(host='build4less.co.uk', port=443): Max retries exceeded with url: /products/iko-enertherm-alu-80mm-x-2-4m-x-1-2m (Caused by ResponseError('too many 429 error responses'))</t>
-  </si>
-  <si>
-    <t>Error: HTTPSConnectionPool(host='build4less.co.uk', port=443): Max retries exceeded with url: /products/iko-enertherm-alu-90mm-x-2-4m-x-1-2m (Caused by ResponseError('too many 429 error responses'))</t>
-  </si>
-  <si>
-    <t>Error: HTTPSConnectionPool(host='build4less.co.uk', port=443): Max retries exceeded with url: /products/iko-enertherm-alu-100mm-x-2-4m-x-1-2m (Caused by ResponseError('too many 429 error responses'))</t>
-  </si>
-  <si>
     <t>£48.85</t>
   </si>
   <si>
-    <t>Error: HTTPSConnectionPool(host='build4less.co.uk', port=443): Max retries exceeded with url: /products/iko-enertherm-alu-120mm-x-2-4m-x-1-2m (Caused by ResponseError('too many 429 error responses'))</t>
-  </si>
-  <si>
-    <t>Error: HTTPSConnectionPool(host='build4less.co.uk', port=443): Max retries exceeded with url: /products/iko-enertherm-alu-140mm-x-2-4m-x-1-2m (Caused by ResponseError('too many 429 error responses'))</t>
-  </si>
-  <si>
-    <t>Error: HTTPSConnectionPool(host='build4less.co.uk', port=443): Max retries exceeded with url: /products/iko-enertherm-alu-150mm-x-2-4m-x-1-2m (Caused by ResponseError('too many 429 error responses'))</t>
-  </si>
-  <si>
-    <t>Error: HTTPSConnectionPool(host='www.building-supplies-online.co.uk', port=443): Max retries exceeded with url: /products/iko-enertherm-alu-2-4m-x-1-2m-all-thicknesses (Caused by ResponseError('too many 429 error responses'))</t>
-  </si>
-  <si>
     <t>£17.99</t>
   </si>
   <si>
-    <t>Error: HTTPSConnectionPool(host='www.building-supplies-online.co.uk', port=443): Max retries exceeded with url: /products/iko-enertherm-alu-2-4m-x-1-2m-all-thicknesses?variant=55643414036864 (Caused by ResponseError('too many 429 error responses'))</t>
-  </si>
-  <si>
-    <t>Error: HTTPSConnectionPool(host='www.building-supplies-online.co.uk', port=443): Max retries exceeded with url: /products/iko-enertherm-alu-2-4m-x-1-2m-all-thicknesses?variant=55643414069632 (Caused by ResponseError('too many 429 error responses'))</t>
-  </si>
-  <si>
-    <t>Error: HTTPSConnectionPool(host='www.building-supplies-online.co.uk', port=443): Max retries exceeded with url: /products/iko-enertherm-alu-2-4m-x-1-2m-all-thicknesses?variant=55643414102400 (Caused by ResponseError('too many 429 error responses'))</t>
-  </si>
-  <si>
-    <t>Error: HTTPSConnectionPool(host='www.building-supplies-online.co.uk', port=443): Max retries exceeded with url: /products/iko-enertherm-alu-2-4m-x-1-2m-all-thicknesses?variant=55643414135168 (Caused by ResponseError('too many 429 error responses'))</t>
-  </si>
-  <si>
-    <t>Error: HTTPSConnectionPool(host='www.building-supplies-online.co.uk', port=443): Max retries exceeded with url: /products/iko-enertherm-alu-2-4m-x-1-2m-all-thicknesses?variant=55643414167936 (Caused by ResponseError('too many 429 error responses'))</t>
-  </si>
-  <si>
-    <t>Error: HTTPSConnectionPool(host='www.building-supplies-online.co.uk', port=443): Max retries exceeded with url: /products/iko-enertherm-alu-2-4m-x-1-2m-all-thicknesses?variant=55643414200704 (Caused by ResponseError('too many 429 error responses'))</t>
-  </si>
-  <si>
-    <t>Error: HTTPSConnectionPool(host='www.building-supplies-online.co.uk', port=443): Max retries exceeded with url: /products/iko-enertherm-alu-2-4m-x-1-2m-all-thicknesses?variant=55643414233472 (Caused by ResponseError('too many 429 error responses'))</t>
-  </si>
-  <si>
     <t>£39.65</t>
   </si>
   <si>
-    <t>Error: HTTPSConnectionPool(host='www.building-supplies-online.co.uk', port=443): Max retries exceeded with url: /products/iko-enertherm-alu-2-4m-x-1-2m-all-thicknesses?variant=55643414299008 (Caused by ResponseError('too many 429 error responses'))</t>
-  </si>
-  <si>
     <t>£49.35</t>
   </si>
   <si>
-    <t>Error: HTTPSConnectionPool(host='www.building-supplies-online.co.uk', port=443): Max retries exceeded with url: /products/iko-enertherm-alu-2-4m-x-1-2m-all-thicknesses?variant=55643414364544 (Caused by ResponseError('too many 429 error responses'))</t>
-  </si>
-  <si>
-    <t>Error: HTTPSConnectionPool(host='www.building-supplies-online.co.uk', port=443): Max retries exceeded with url: /products/iko-enertherm-alu-2-4m-x-1-2m-all-thicknesses?variant=55643414397312 (Caused by ResponseError('too many 429 error responses'))</t>
-  </si>
-  <si>
     <t>£16.92</t>
   </si>
   <si>
@@ -302,13 +203,34 @@
   </si>
   <si>
     <t>POA</t>
+  </si>
+  <si>
+    <t>£15.25</t>
+  </si>
+  <si>
+    <t>£29.80</t>
+  </si>
+  <si>
+    <t>£32.65</t>
+  </si>
+  <si>
+    <t>£32.75</t>
+  </si>
+  <si>
+    <t>£40.15</t>
+  </si>
+  <si>
+    <t>£59.99</t>
+  </si>
+  <si>
+    <t>£59.45</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -371,13 +293,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -415,7 +345,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -449,6 +379,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -483,9 +414,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -658,11 +590,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K15"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -697,7 +629,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>11</v>
       </c>
@@ -705,34 +637,34 @@
         <v>25</v>
       </c>
       <c r="C2" t="s">
-        <v>39</v>
+        <v>61</v>
       </c>
       <c r="D2" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="E2" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="F2" t="s">
-        <v>81</v>
+        <v>46</v>
       </c>
       <c r="G2" t="s">
-        <v>95</v>
+        <v>60</v>
       </c>
       <c r="H2" t="s">
-        <v>91</v>
+        <v>56</v>
       </c>
       <c r="I2" t="s">
-        <v>95</v>
+        <v>60</v>
       </c>
       <c r="J2" t="s">
-        <v>95</v>
+        <v>60</v>
       </c>
       <c r="K2" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -740,34 +672,34 @@
         <v>26</v>
       </c>
       <c r="C3" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="D3" t="s">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="E3" t="s">
-        <v>68</v>
+        <v>43</v>
       </c>
       <c r="F3" t="s">
-        <v>82</v>
+        <v>47</v>
       </c>
       <c r="G3" t="s">
-        <v>95</v>
+        <v>60</v>
       </c>
       <c r="H3" t="s">
-        <v>91</v>
+        <v>56</v>
       </c>
       <c r="I3" t="s">
-        <v>95</v>
+        <v>60</v>
       </c>
       <c r="J3" t="s">
-        <v>95</v>
+        <v>60</v>
       </c>
       <c r="K3" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>13</v>
       </c>
@@ -775,34 +707,34 @@
         <v>27</v>
       </c>
       <c r="C4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D4" t="s">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="E4" t="s">
-        <v>69</v>
+        <v>39</v>
       </c>
       <c r="F4" t="s">
-        <v>83</v>
+        <v>48</v>
       </c>
       <c r="G4" t="s">
-        <v>95</v>
+        <v>60</v>
       </c>
       <c r="H4" t="s">
-        <v>91</v>
+        <v>56</v>
       </c>
       <c r="I4" t="s">
-        <v>95</v>
+        <v>60</v>
       </c>
       <c r="J4" t="s">
-        <v>95</v>
+        <v>60</v>
       </c>
       <c r="K4" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>14</v>
       </c>
@@ -810,34 +742,34 @@
         <v>28</v>
       </c>
       <c r="C5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D5" t="s">
-        <v>56</v>
+        <v>40</v>
       </c>
       <c r="E5" t="s">
-        <v>70</v>
+        <v>40</v>
       </c>
       <c r="F5" t="s">
-        <v>84</v>
+        <v>49</v>
       </c>
       <c r="G5" t="s">
-        <v>95</v>
+        <v>60</v>
       </c>
       <c r="H5" t="s">
-        <v>91</v>
+        <v>56</v>
       </c>
       <c r="I5" t="s">
-        <v>95</v>
+        <v>60</v>
       </c>
       <c r="J5" t="s">
-        <v>95</v>
+        <v>60</v>
       </c>
       <c r="K5" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>15</v>
       </c>
@@ -845,34 +777,34 @@
         <v>29</v>
       </c>
       <c r="C6" t="s">
-        <v>43</v>
+        <v>62</v>
       </c>
       <c r="D6" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="E6" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="F6" t="s">
-        <v>85</v>
+        <v>50</v>
       </c>
       <c r="G6" t="s">
-        <v>95</v>
+        <v>60</v>
       </c>
       <c r="H6" t="s">
-        <v>91</v>
+        <v>56</v>
       </c>
       <c r="I6" t="s">
-        <v>95</v>
+        <v>60</v>
       </c>
       <c r="J6" t="s">
-        <v>95</v>
+        <v>60</v>
       </c>
       <c r="K6" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>16</v>
       </c>
@@ -880,34 +812,34 @@
         <v>30</v>
       </c>
       <c r="C7" t="s">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="D7" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="E7" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="F7" t="s">
-        <v>86</v>
+        <v>51</v>
       </c>
       <c r="G7" t="s">
-        <v>95</v>
+        <v>60</v>
       </c>
       <c r="H7" t="s">
-        <v>91</v>
+        <v>56</v>
       </c>
       <c r="I7" t="s">
-        <v>95</v>
+        <v>60</v>
       </c>
       <c r="J7" t="s">
-        <v>95</v>
+        <v>60</v>
       </c>
       <c r="K7" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>17</v>
       </c>
@@ -915,34 +847,34 @@
         <v>31</v>
       </c>
       <c r="C8" t="s">
-        <v>45</v>
+        <v>64</v>
       </c>
       <c r="D8" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="E8" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="F8" t="s">
-        <v>87</v>
+        <v>52</v>
       </c>
       <c r="G8" t="s">
-        <v>95</v>
+        <v>60</v>
       </c>
       <c r="H8" t="s">
-        <v>91</v>
+        <v>56</v>
       </c>
       <c r="I8" t="s">
-        <v>95</v>
+        <v>60</v>
       </c>
       <c r="J8" t="s">
-        <v>95</v>
+        <v>60</v>
       </c>
       <c r="K8" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>18</v>
       </c>
@@ -950,34 +882,34 @@
         <v>32</v>
       </c>
       <c r="C9" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="D9" t="s">
-        <v>60</v>
+        <v>41</v>
       </c>
       <c r="E9" t="s">
-        <v>74</v>
+        <v>41</v>
       </c>
       <c r="F9" t="s">
-        <v>88</v>
+        <v>53</v>
       </c>
       <c r="G9" t="s">
-        <v>95</v>
+        <v>60</v>
       </c>
       <c r="H9" t="s">
-        <v>91</v>
+        <v>56</v>
       </c>
       <c r="I9" t="s">
-        <v>95</v>
+        <v>60</v>
       </c>
       <c r="J9" t="s">
-        <v>95</v>
+        <v>60</v>
       </c>
       <c r="K9" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>19</v>
       </c>
@@ -985,34 +917,34 @@
         <v>33</v>
       </c>
       <c r="C10" t="s">
-        <v>47</v>
+        <v>65</v>
       </c>
       <c r="D10" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="E10" t="s">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="F10" t="s">
-        <v>89</v>
+        <v>54</v>
       </c>
       <c r="G10" t="s">
-        <v>95</v>
+        <v>60</v>
       </c>
       <c r="H10" t="s">
-        <v>91</v>
+        <v>56</v>
       </c>
       <c r="I10" t="s">
-        <v>95</v>
+        <v>60</v>
       </c>
       <c r="J10" t="s">
-        <v>95</v>
+        <v>60</v>
       </c>
       <c r="K10" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>20</v>
       </c>
@@ -1020,34 +952,34 @@
         <v>34</v>
       </c>
       <c r="C11" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="D11" t="s">
-        <v>62</v>
+        <v>44</v>
       </c>
       <c r="E11" t="s">
-        <v>76</v>
+        <v>44</v>
       </c>
       <c r="F11" t="s">
-        <v>90</v>
+        <v>55</v>
       </c>
       <c r="G11" t="s">
-        <v>95</v>
+        <v>60</v>
       </c>
       <c r="H11" t="s">
-        <v>91</v>
+        <v>56</v>
       </c>
       <c r="I11" t="s">
-        <v>95</v>
+        <v>60</v>
       </c>
       <c r="J11" t="s">
-        <v>95</v>
+        <v>60</v>
       </c>
       <c r="K11" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>21</v>
       </c>
@@ -1055,34 +987,34 @@
         <v>35</v>
       </c>
       <c r="C12" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="D12" t="s">
-        <v>63</v>
+        <v>42</v>
       </c>
       <c r="E12" t="s">
-        <v>77</v>
+        <v>42</v>
       </c>
       <c r="F12" t="s">
-        <v>91</v>
+        <v>56</v>
       </c>
       <c r="G12" t="s">
-        <v>91</v>
+        <v>56</v>
       </c>
       <c r="H12" t="s">
-        <v>91</v>
+        <v>56</v>
       </c>
       <c r="I12" t="s">
-        <v>95</v>
+        <v>60</v>
       </c>
       <c r="J12" t="s">
-        <v>95</v>
+        <v>60</v>
       </c>
       <c r="K12" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>22</v>
       </c>
@@ -1090,34 +1022,34 @@
         <v>36</v>
       </c>
       <c r="C13" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="D13" t="s">
-        <v>64</v>
+        <v>45</v>
       </c>
       <c r="E13" t="s">
-        <v>78</v>
+        <v>45</v>
       </c>
       <c r="F13" t="s">
-        <v>92</v>
+        <v>57</v>
       </c>
       <c r="G13" t="s">
-        <v>95</v>
+        <v>60</v>
       </c>
       <c r="H13" t="s">
-        <v>91</v>
+        <v>56</v>
       </c>
       <c r="I13" t="s">
-        <v>95</v>
+        <v>60</v>
       </c>
       <c r="J13" t="s">
-        <v>95</v>
+        <v>60</v>
       </c>
       <c r="K13" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>23</v>
       </c>
@@ -1125,34 +1057,34 @@
         <v>37</v>
       </c>
       <c r="C14" t="s">
-        <v>51</v>
+        <v>66</v>
       </c>
       <c r="D14" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E14" t="s">
-        <v>79</v>
+        <v>66</v>
       </c>
       <c r="F14" t="s">
-        <v>93</v>
+        <v>58</v>
       </c>
       <c r="G14" t="s">
-        <v>95</v>
+        <v>60</v>
       </c>
       <c r="H14" t="s">
-        <v>91</v>
+        <v>56</v>
       </c>
       <c r="I14" t="s">
-        <v>95</v>
+        <v>60</v>
       </c>
       <c r="J14" t="s">
-        <v>95</v>
+        <v>60</v>
       </c>
       <c r="K14" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>24</v>
       </c>
@@ -1160,31 +1092,31 @@
         <v>38</v>
       </c>
       <c r="C15" t="s">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="D15" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E15" t="s">
-        <v>80</v>
+        <v>67</v>
       </c>
       <c r="F15" t="s">
-        <v>94</v>
+        <v>59</v>
       </c>
       <c r="G15" t="s">
-        <v>95</v>
+        <v>60</v>
       </c>
       <c r="H15" t="s">
-        <v>91</v>
+        <v>56</v>
       </c>
       <c r="I15" t="s">
-        <v>95</v>
+        <v>60</v>
       </c>
       <c r="J15" t="s">
-        <v>95</v>
+        <v>60</v>
       </c>
       <c r="K15" t="s">
-        <v>95</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>
